--- a/src/main/resources/python/MultifacetedModeling/RuleExtraction/SVR/data.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/RuleExtraction/SVR/data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="suport_vector" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="class" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data-similar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="knowledge-similar" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prediction" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="label" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="org_label" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="suport_vector" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="class" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="data-similar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="knowledge-similar" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="prediction" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="label" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="org_label" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'suport_vector'!$C$1:$C$89</definedName>
@@ -6569,10 +6569,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="T1:T2"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="T1:T2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -12816,12 +12816,12 @@
   </sheetData>
   <autoFilter ref="C1:C89"/>
   <mergeCells count="6">
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="U1:U2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="V1:V2"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -19523,20 +19523,20 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="W1:W2"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="Y66:Y87"/>
     <mergeCell ref="X49:X65"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="X24:X48"/>
+    <mergeCell ref="X66:X87"/>
+    <mergeCell ref="Y49:Y65"/>
     <mergeCell ref="X3:X23"/>
-    <mergeCell ref="X66:X87"/>
     <mergeCell ref="Y3:Y23"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="T1:T2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="Y66:Y87"/>
-    <mergeCell ref="Y49:Y65"/>
+    <mergeCell ref="X24:X48"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="Y24:Y48"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -22955,11 +22955,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="U1:U2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23352,595 +23352,595 @@
     <row r="2">
       <c r="A2" s="119" t="inlineStr">
         <is>
-          <t>21.604320862723988</t>
+          <t>76.02150920061305</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="119" t="inlineStr">
         <is>
-          <t>25.100306520923446</t>
+          <t>75.36640335266392</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="119" t="inlineStr">
         <is>
-          <t>23.686451016109082</t>
+          <t>65.64082200047244</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="119" t="inlineStr">
         <is>
-          <t>24.843869712864468</t>
+          <t>44.128288925904705</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="119" t="inlineStr">
         <is>
-          <t>26.927367909035432</t>
+          <t>53.623042649253655</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="119" t="inlineStr">
         <is>
-          <t>32.916877493406496</t>
+          <t>77.36040141526976</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="119" t="inlineStr">
         <is>
-          <t>37.240478504597654</t>
+          <t>68.47184519673777</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="119" t="inlineStr">
         <is>
-          <t>38.418842379628565</t>
+          <t>80.78997239146094</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
         <is>
-          <t>25.361363608231365</t>
+          <t>75.28957346711206</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="119" t="inlineStr">
         <is>
-          <t>25.099766185470124</t>
+          <t>59.59614791669343</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="119" t="inlineStr">
         <is>
-          <t>24.899878610859567</t>
+          <t>80.58857886546389</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="119" t="inlineStr">
         <is>
-          <t>24.017091476427687</t>
+          <t>85.3142617330488</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="119" t="inlineStr">
         <is>
-          <t>26.400118115677266</t>
+          <t>83.1940946248011</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="119" t="inlineStr">
         <is>
-          <t>25.802832218692565</t>
+          <t>68.6750231661843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="119" t="inlineStr">
         <is>
-          <t>27.539085678257045</t>
+          <t>35.03264925726024</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="119" t="inlineStr">
         <is>
-          <t>26.942441534182414</t>
+          <t>43.60850770783629</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
         <is>
-          <t>27.578085275711665</t>
+          <t>39.5400159425302</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="119" t="inlineStr">
         <is>
-          <t>27.031575212465548</t>
+          <t>30.327620414064647</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="119" t="inlineStr">
         <is>
-          <t>19.108262284654735</t>
+          <t>47.28887848712187</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="119" t="inlineStr">
         <is>
-          <t>19.41848028949483</t>
+          <t>44.58932983922069</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="119" t="inlineStr">
         <is>
-          <t>33.351713720707956</t>
+          <t>48.548740163427546</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="119" t="inlineStr">
         <is>
-          <t>26.600188631973303</t>
+          <t>68.31074024986086</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="119" t="inlineStr">
         <is>
-          <t>27.515306821880436</t>
+          <t>71.70630509150772</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="119" t="inlineStr">
         <is>
-          <t>27.54085353530882</t>
+          <t>71.64780619983142</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="119" t="inlineStr">
         <is>
-          <t>42.51646257549316</t>
+          <t>103.58179527885775</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="119" t="inlineStr">
         <is>
-          <t>34.47071911552354</t>
+          <t>103.41701392191624</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="119" t="inlineStr">
         <is>
-          <t>28.702131115707424</t>
+          <t>32.58173663816432</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="119" t="inlineStr">
         <is>
-          <t>25.10005649465503</t>
+          <t>31.989644880005308</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="119" t="inlineStr">
         <is>
-          <t>25.883675035031267</t>
+          <t>32.325021862707594</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="119" t="inlineStr">
         <is>
-          <t>27.290442824101966</t>
+          <t>32.95391022026717</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="119" t="inlineStr">
         <is>
-          <t>28.812412453148788</t>
+          <t>32.8837906085973</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="119" t="inlineStr">
         <is>
-          <t>30.169477458702694</t>
+          <t>33.56970604373236</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="119" t="inlineStr">
         <is>
-          <t>26.632371128057407</t>
+          <t>113.1372988735585</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="119" t="inlineStr">
         <is>
-          <t>24.573109671209856</t>
+          <t>99.69315563592593</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="119" t="inlineStr">
         <is>
-          <t>25.72917323431492</t>
+          <t>97.96078065660885</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="119" t="inlineStr">
         <is>
-          <t>26.017828287280558</t>
+          <t>96.25282617582963</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="119" t="inlineStr">
         <is>
-          <t>25.596992138801248</t>
+          <t>95.97900520486291</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="119" t="inlineStr">
         <is>
-          <t>26.7139297100532</t>
+          <t>92.64195532337038</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="119" t="inlineStr">
         <is>
-          <t>25.705150816150514</t>
+          <t>93.0847387422101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="119" t="inlineStr">
         <is>
-          <t>24.900382224204442</t>
+          <t>89.83539108747061</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="119" t="inlineStr">
         <is>
-          <t>26.419745909007666</t>
+          <t>69.48422363781648</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="119" t="inlineStr">
         <is>
-          <t>25.09964637447323</t>
+          <t>79.75934811882686</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="119" t="inlineStr">
         <is>
-          <t>19.65597562006638</t>
+          <t>73.58426234233323</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="119" t="inlineStr">
         <is>
-          <t>21.394461868106056</t>
+          <t>83.63425206157913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="119" t="inlineStr">
         <is>
-          <t>25.696638632923786</t>
+          <t>30.957567272103383</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="119" t="inlineStr">
         <is>
-          <t>23.183861406528315</t>
+          <t>42.91772136357482</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="119" t="inlineStr">
         <is>
-          <t>23.409770788571485</t>
+          <t>45.42199646247722</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="119" t="inlineStr">
         <is>
-          <t>24.271599951218427</t>
+          <t>47.15024586194951</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="119" t="inlineStr">
         <is>
-          <t>24.369569193911396</t>
+          <t>49.421086800818394</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="119" t="inlineStr">
         <is>
-          <t>24.832945984957227</t>
+          <t>50.325450100964396</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="119" t="inlineStr">
         <is>
-          <t>40.72825286403725</t>
+          <t>98.1564167206331</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="119" t="inlineStr">
         <is>
-          <t>26.752453033576835</t>
+          <t>31.850706098433953</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="119" t="inlineStr">
         <is>
-          <t>32.857553789653544</t>
+          <t>77.2092128907457</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="119" t="inlineStr">
         <is>
-          <t>33.93754651322269</t>
+          <t>77.95182548805582</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="119" t="inlineStr">
         <is>
-          <t>25.411533251519536</t>
+          <t>14.691438797753598</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="119" t="inlineStr">
         <is>
-          <t>20.655836051931082</t>
+          <t>79.63092906243972</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="119" t="inlineStr">
         <is>
-          <t>27.38769163861938</t>
+          <t>40.987652572846564</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="119" t="inlineStr">
         <is>
-          <t>42.366503415408765</t>
+          <t>102.05936499764618</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="119" t="inlineStr">
         <is>
-          <t>42.28182334958864</t>
+          <t>104.87505415865229</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="119" t="inlineStr">
         <is>
-          <t>42.16207733115589</t>
+          <t>103.92128130514698</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="119" t="inlineStr">
         <is>
-          <t>39.57047409643635</t>
+          <t>98.36217743287347</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="119" t="inlineStr">
         <is>
-          <t>26.899059943988142</t>
+          <t>73.2556065453588</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="119" t="inlineStr">
         <is>
-          <t>26.17266564474364</t>
+          <t>78.88420357046775</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="119" t="inlineStr">
         <is>
-          <t>28.133649608349252</t>
+          <t>53.81792275390678</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="119" t="inlineStr">
         <is>
-          <t>30.264279974864145</t>
+          <t>55.6102834296206</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="119" t="inlineStr">
         <is>
-          <t>31.91744843745105</t>
+          <t>56.75367654696107</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="119" t="inlineStr">
         <is>
-          <t>33.27055598390279</t>
+          <t>57.16965427497049</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="119" t="inlineStr">
         <is>
-          <t>26.676886562551154</t>
+          <t>51.44290292538995</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="119" t="inlineStr">
         <is>
-          <t>25.10039022021696</t>
+          <t>44.867329835267135</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="119" t="inlineStr">
         <is>
-          <t>31.519713678708804</t>
+          <t>37.1753924943257</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="119" t="inlineStr">
         <is>
-          <t>36.36292362266098</t>
+          <t>26.962834466441485</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="119" t="inlineStr">
         <is>
-          <t>26.522509603702595</t>
+          <t>50.3756939160346</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="119" t="inlineStr">
         <is>
-          <t>41.469870934955175</t>
+          <t>103.23156245778972</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="119" t="inlineStr">
         <is>
-          <t>40.64884815917517</t>
+          <t>104.91828361420221</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="119" t="inlineStr">
         <is>
-          <t>28.748898691585488</t>
+          <t>71.80545589266382</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="119" t="inlineStr">
         <is>
-          <t>30.46246523894218</t>
+          <t>82.15151779285256</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="119" t="inlineStr">
         <is>
-          <t>28.48021037468377</t>
+          <t>67.86103111175686</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="119" t="inlineStr">
         <is>
-          <t>25.099418162570664</t>
+          <t>34.68337353808793</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="119" t="inlineStr">
         <is>
-          <t>26.338536536417188</t>
+          <t>40.73924093249094</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="119" t="inlineStr">
         <is>
-          <t>25.099786793914866</t>
+          <t>27.25643578034518</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="119" t="inlineStr">
         <is>
-          <t>26.640822204188176</t>
+          <t>54.63715717628647</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="119" t="inlineStr">
         <is>
-          <t>26.98433246868253</t>
+          <t>54.65192591313866</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="119" t="inlineStr">
         <is>
-          <t>25.09993284936592</t>
+          <t>48.09165857089348</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="119" t="inlineStr">
         <is>
-          <t>22.504169297037784</t>
+          <t>71.60321717698676</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="119" t="inlineStr">
         <is>
-          <t>26.01021738155979</t>
+          <t>95.93663944900413</t>
         </is>
       </c>
     </row>
@@ -24680,35 +24680,35 @@
     <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -24736,35 +24736,35 @@
     <row r="10">
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -24778,21 +24778,21 @@
     <row r="16">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -24806,21 +24806,21 @@
     <row r="20">
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -24911,49 +24911,49 @@
     <row r="35">
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -24967,7 +24967,7 @@
     <row r="43">
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
     <row r="45">
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -24995,35 +24995,35 @@
     <row r="47">
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -25065,14 +25065,14 @@
     <row r="57">
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -25107,56 +25107,56 @@
     <row r="63">
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
     <row r="73">
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -25198,14 +25198,14 @@
     <row r="76">
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
     <row r="80">
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -25240,35 +25240,35 @@
     <row r="82">
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
